--- a/data/trans_camb/P16A13-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,46</t>
+          <t>1,55; 5,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,33</t>
+          <t>0,95; 4,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 11,77</t>
+          <t>6,29; 11,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 4,01</t>
+          <t>-0,16; 3,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,9</t>
+          <t>-0,07; 4,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,55</t>
+          <t>7,4; 11,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,98</t>
+          <t>1,21; 3,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,51</t>
+          <t>0,82; 3,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 10,9</t>
+          <t>7,47; 10,82</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,52; 973,93</t>
+          <t>73,98; 830,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42,19; 740,72</t>
+          <t>38,69; 657,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>338,75; 1914,27</t>
+          <t>309,25; 1806,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 188,81</t>
+          <t>-8,28; 172,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 200,42</t>
+          <t>-6,06; 189,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>173,19; 581,58</t>
+          <t>175,02; 566,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,61; 259,17</t>
+          <t>45,18; 251,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,33; 225,06</t>
+          <t>29,95; 209,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>260,05; 683,7</t>
+          <t>274,43; 703,44</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,49</t>
+          <t>-0,89; 2,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,21</t>
+          <t>-1,81; 1,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,64</t>
+          <t>-1,68; 2,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 4,08</t>
+          <t>0,35; 4,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,97</t>
+          <t>-1,36; 1,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,49</t>
+          <t>4,02; 7,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,65</t>
+          <t>0,31; 2,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,1</t>
+          <t>-1,09; 1,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,41</t>
+          <t>0,78; 4,46</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,3; 102,25</t>
+          <t>-24,99; 92,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,4; 49,39</t>
+          <t>-43,68; 48,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,33; 99,59</t>
+          <t>-35,39; 106,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,71; 174,31</t>
+          <t>6,42; 180,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 86,21</t>
+          <t>-33,39; 85,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,19; 329,62</t>
+          <t>91,19; 344,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,39; 104,03</t>
+          <t>6,27; 108,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 44,55</t>
+          <t>-29,92; 46,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,47; 165,28</t>
+          <t>26,84; 174,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,81</t>
+          <t>-2,05; 1,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 1,07</t>
+          <t>-2,71; 1,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,43</t>
+          <t>-0,95; 3,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,44</t>
+          <t>-1,99; 2,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,74</t>
+          <t>-2,61; 1,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,79</t>
+          <t>-3,53; 1,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,61</t>
+          <t>-1,21; 1,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,8</t>
+          <t>-2,03; 0,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,83</t>
+          <t>-1,46; 1,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 70,35</t>
+          <t>-45,23; 65,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 43,86</t>
+          <t>-57,81; 43,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,52; 127,11</t>
+          <t>-22,66; 115,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,66; 70,91</t>
+          <t>-35,48; 71,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,51; 50,81</t>
+          <t>-47,35; 42,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,22; 47,38</t>
+          <t>-55,52; 41,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,88; 47,44</t>
+          <t>-25,11; 48,17</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,5; 23,38</t>
+          <t>-42,26; 23,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 51,88</t>
+          <t>-29,01; 53,0</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,07</t>
+          <t>0,27; 4,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,51</t>
+          <t>-1,48; 1,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,34</t>
+          <t>2,43; 6,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,58</t>
+          <t>0,6; 4,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,39</t>
+          <t>-1,39; 2,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,15</t>
+          <t>1,44; 5,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,61</t>
+          <t>1,02; 3,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,47</t>
+          <t>-0,84; 1,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,31</t>
+          <t>2,46; 5,04</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 223,16</t>
+          <t>4,35; 219,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,21; 86,67</t>
+          <t>-44,68; 83,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76,03; 373,93</t>
+          <t>72,36; 337,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,74; 160,9</t>
+          <t>10,46; 151,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 80,27</t>
+          <t>-29,97; 69,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,54; 178,48</t>
+          <t>29,78; 174,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,0; 139,54</t>
+          <t>27,32; 140,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 56,44</t>
+          <t>-22,91; 58,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66,25; 214,28</t>
+          <t>61,85; 187,94</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,47</t>
+          <t>0,49; 2,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,15</t>
+          <t>-0,51; 1,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,48</t>
+          <t>1,83; 4,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,78</t>
+          <t>0,69; 2,79</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,39</t>
+          <t>-0,44; 1,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,66; 5,28</t>
+          <t>2,74; 5,29</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,27</t>
+          <t>1,01; 2,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,05</t>
+          <t>-0,21; 0,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,64</t>
+          <t>2,81; 4,59</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>21,4; 109,54</t>
+          <t>14,96; 110,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 47,88</t>
+          <t>-17,3; 52,04</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69,24; 203,3</t>
+          <t>61,79; 199,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,56; 86,16</t>
+          <t>17,18; 89,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 43,52</t>
+          <t>-11,1; 47,18</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,34; 164,69</t>
+          <t>73,61; 169,91</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,56; 81,8</t>
+          <t>28,91; 83,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 37,34</t>
+          <t>-6,53; 34,88</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>87,23; 167,78</t>
+          <t>84,02; 158,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A13-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P16A13-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8,61</t>
+          <t>7,67</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>9,24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9,13</t>
+          <t>8,5</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,55</t>
+          <t>1,77; 5,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,29</t>
+          <t>1,0; 4,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 11,92</t>
+          <t>5,77; 9,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,69</t>
+          <t>-0,4; 3,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,17</t>
+          <t>-0,34; 3,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 11,53</t>
+          <t>7,07; 11,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,9</t>
+          <t>1,22; 3,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,4</t>
+          <t>0,94; 3,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 10,82</t>
+          <t>7,11; 10,12</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>743,48%</t>
+          <t>661,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>324,73%</t>
+          <t>313,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>445,81%</t>
+          <t>415,16%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>73,98; 830,49</t>
+          <t>91,01; 821,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,69; 657,69</t>
+          <t>34,49; 682,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>309,25; 1806,01</t>
+          <t>276,65; 1628,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 172,0</t>
+          <t>-12,77; 174,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 189,35</t>
+          <t>-13,33; 176,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>175,02; 566,7</t>
+          <t>162,44; 578,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,18; 251,83</t>
+          <t>45,33; 254,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,95; 209,6</t>
+          <t>29,78; 219,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>274,43; 703,44</t>
+          <t>265,91; 672,15</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,76</t>
+          <t>5,59</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,33</t>
+          <t>-0,94; 2,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,18</t>
+          <t>-1,95; 1,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,69</t>
+          <t>0,3; 3,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,18</t>
+          <t>0,37; 4,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,97</t>
+          <t>-1,36; 1,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,02; 7,57</t>
+          <t>3,75; 7,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,76</t>
+          <t>0,15; 2,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,17</t>
+          <t>-1,11; 1,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,46</t>
+          <t>2,58; 4,91</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>186,63%</t>
+          <t>180,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>120,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 92,71</t>
+          <t>-26,31; 114,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 48,06</t>
+          <t>-47,81; 58,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-35,39; 106,31</t>
+          <t>4,2; 155,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,42; 180,48</t>
+          <t>7,42; 173,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,39; 85,75</t>
+          <t>-35,39; 85,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,19; 344,35</t>
+          <t>89,87; 325,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 108,07</t>
+          <t>3,74; 98,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 46,36</t>
+          <t>-30,36; 43,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,84; 174,05</t>
+          <t>64,1; 187,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>1,0</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 1,85</t>
+          <t>-2,02; 2,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,06</t>
+          <t>-2,93; 1,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,08</t>
+          <t>-1,15; 3,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,55</t>
+          <t>-2,03; 2,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,53</t>
+          <t>-2,55; 1,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,61</t>
+          <t>-1,33; 2,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,6</t>
+          <t>-1,4; 1,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,78</t>
+          <t>-2,02; 0,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,8</t>
+          <t>-0,38; 2,48</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-10,09%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 65,82</t>
+          <t>-42,76; 82,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 43,48</t>
+          <t>-59,5; 51,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 115,67</t>
+          <t>-23,71; 120,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,48; 71,35</t>
+          <t>-34,82; 75,64</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 42,21</t>
+          <t>-45,92; 50,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,52; 41,13</t>
+          <t>-23,06; 79,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 48,17</t>
+          <t>-28,66; 48,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 23,5</t>
+          <t>-41,73; 22,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-29,01; 53,0</t>
+          <t>-8,64; 74,38</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,32</t>
+          <t>4,29</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>4,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 4,06</t>
+          <t>0,28; 3,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,43</t>
+          <t>-1,34; 1,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,03</t>
+          <t>2,54; 5,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,49</t>
+          <t>0,56; 4,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,18</t>
+          <t>-1,18; 2,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,21</t>
+          <t>2,48; 5,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,56</t>
+          <t>0,94; 3,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,54</t>
+          <t>-0,88; 1,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,04</t>
+          <t>2,84; 5,33</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>175,25%</t>
+          <t>173,81%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>102,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119,88%</t>
+          <t>128,56%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,35; 219,31</t>
+          <t>3,31; 206,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,68; 83,55</t>
+          <t>-42,77; 94,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72,36; 337,42</t>
+          <t>72,9; 342,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,46; 151,06</t>
+          <t>9,37; 135,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,97; 69,63</t>
+          <t>-27,49; 82,85</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,78; 174,3</t>
+          <t>49,96; 193,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,32; 140,17</t>
+          <t>21,57; 136,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 58,18</t>
+          <t>-24,06; 59,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>61,85; 187,94</t>
+          <t>71,29; 202,36</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,37</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>4,78</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>4,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,4</t>
+          <t>0,56; 2,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,15</t>
+          <t>-0,56; 1,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,4</t>
+          <t>2,66; 4,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,79</t>
+          <t>0,73; 2,76</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,48</t>
+          <t>-0,54; 1,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,29</t>
+          <t>3,83; 5,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,36</t>
+          <t>0,93; 2,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,99</t>
+          <t>-0,25; 0,99</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,59</t>
+          <t>3,53; 4,86</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>127,61%</t>
+          <t>136,02%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>117,89%</t>
+          <t>133,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>122,29%</t>
+          <t>134,71%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>14,96; 110,7</t>
+          <t>18,95; 101,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 52,04</t>
+          <t>-18,65; 47,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>61,79; 199,35</t>
+          <t>85,67; 201,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17,18; 89,73</t>
+          <t>16,06; 87,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 47,18</t>
+          <t>-13,82; 42,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,61; 169,91</t>
+          <t>93,52; 180,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,91; 83,67</t>
+          <t>26,45; 81,36</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 34,88</t>
+          <t>-7,89; 34,46</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>84,02; 158,33</t>
+          <t>103,95; 172,45</t>
         </is>
       </c>
     </row>
